--- a/data/raw/Arens_RWC_limits_JK+run4ELYRHI.xlsx
+++ b/data/raw/Arens_RWC_limits_JK+run4ELYRHI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Work\Masters\Minimum Conductance\Huw_min_cond (working ver)\Projected Leaf area versions\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/01424892_wf_uct_ac_za/Documents/Adam Data OneDrive/Adam Manuscripts/irlam/gmin_methodology_paper-main/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB93ECF3-05FF-4FCC-A7B1-6AD00F0E98CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DEBA1CF1-1C24-42B4-A82B-AA7DCE75CAE8}"/>
+    <workbookView xWindow="77900" yWindow="600" windowWidth="23200" windowHeight="13480" xr2:uid="{DEBA1CF1-1C24-42B4-A82B-AA7DCE75CAE8}"/>
   </bookViews>
   <sheets>
     <sheet name="RWC_limits_JK" sheetId="1" r:id="rId1"/>
@@ -5122,22 +5122,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC75071B-1DF9-4588-8659-FDEFE1E0B0D7}">
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="2"/>
-    <col min="5" max="5" width="10.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="2"/>
-    <col min="13" max="13" width="8.7265625" style="2"/>
-    <col min="14" max="14" width="12.36328125" customWidth="1"/>
-    <col min="15" max="15" width="12.26953125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.7265625" style="14"/>
-    <col min="23" max="23" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="2"/>
+    <col min="5" max="5" width="10.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" style="2"/>
+    <col min="13" max="13" width="8.6640625" style="2"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.6640625" style="14"/>
+    <col min="23" max="23" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>0.29653094199657642</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>0.78142713593189383</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>0.14317821063276354</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>6.4979876430006633E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="80.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" ht="80.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>49</v>
       </c>
@@ -5578,7 +5578,7 @@
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B7">
         <f>-1/(((-D2+100)*-0.6637)+5.8537)</f>
         <v>5.2601364949388802</v>
@@ -5590,7 +5590,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>38</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>0.77800000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>81.18308847839009</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>45</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>-2.2649927987980014</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>47</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>46</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" t="s">
         <v>9</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="12" t="s">
         <v>44</v>
       </c>
@@ -5756,14 +5756,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D45F37FE-F83D-4C80-8285-DA98828E2B09}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5771,7 +5771,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0.27149520901773999</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>5.6703302010060197</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1.4932143286203701</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>4.8791214761317701</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2.7149334482229999</v>
       </c>
@@ -5795,7 +5795,7 @@
         <v>4.0000010060739104</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4.0723970653421198</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>3.1648348994969799</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5.0226271899118</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>2.5494516771378</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5.8371066029802199</v>
       </c>
@@ -5819,7 +5819,7 @@
         <v>2.0219791938883001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6.7873367275499099</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>1.31868120812374</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7.6018161406183298</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>12.0814529124946</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>0.659340604061872</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>15.4751088483</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>0.52747248324949803</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>18.1900485105078</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>0.43956174413980797</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>21.990944152847401</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>0.35164899288227802</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>24.8416220985869</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>0.26373624162474901</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>27.5565617607947</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
       <c r="F17">
         <v>91.649745290553199</v>
       </c>
@@ -5917,14 +5917,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6985EF5A-0869-46E9-B6D8-2237B4381CE8}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0.13636153670411599</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>7.8688524590163897</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1.7727249460775301</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>7.1693995741547099</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2.8636359664034798</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>6.6448094102202804</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4.6363609124809999</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>5.8142069832223298</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6.2727243218544197</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>5.1147540983606499</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>8.04544926793195</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>4.2841536725153597</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>10.636362160927201</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>3.1038258036629101</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>12.4090933492357</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>2.3169405577612698</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>13.7727212007389</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>1.6174856717469199</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>15.5454523890474</v>
       </c>
@@ -6015,7 +6015,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>18.545456134386001</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>0.74317006595799096</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>20.0454517648243</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>0.69945288486168</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>22.3636290999493</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>84.454547610952602</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>24.681818919536301</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>0.56830534387807297</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>26.7272731812531</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>0.52459016393442603</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>29.181818295313199</v>
       </c>
@@ -6076,14 +6076,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EE3745-D59F-4FFE-9E58-A0B079FE39DA}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2.0454542617167699</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>7.4725273840813902</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2.59090665076423</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>6.9890121609215603</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3.5454498921550601</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>6.15384584428487</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4.2272700601376503</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>5.5824158356074802</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4.9090902281202498</v>
       </c>
@@ -6131,7 +6131,7 @@
         <v>5.0549432196888704</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5.7272719328069597</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>4.35164908132852</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6.5454536374936696</v>
       </c>
@@ -6147,7 +6147,7 @@
         <v>3.6923083114302599</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7.3636353421803804</v>
       </c>
@@ -6155,7 +6155,7 @@
         <v>2.9010993875523399</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8.1818170468670903</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>2.2857119861161701</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>8.7272756781455794</v>
       </c>
@@ -6171,7 +6171,7 @@
         <v>1.80219676295634</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>9.6818126773053699</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>10.9090852343354</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>0.96703044631965496</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13.2272750539224</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>90.318187322694627</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15.818175462455599</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>0.79120892387791297</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>18.1363652820427</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>0.70329413836035004</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>21.818182953132901</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>0.61538337713947899</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>23.727269435914501</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>0.52747261591860795</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>25.2272650663528</v>
       </c>
@@ -6242,7 +6242,7 @@
         <v>0.48351522315982698</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>27.272719328069599</v>
       </c>
@@ -6250,7 +6250,7 @@
         <v>0.39560446193895599</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>29.181818295313199</v>
       </c>
